--- a/product_upload/packages/13/file.xlsx
+++ b/product_upload/packages/13/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>CLARITT 125 MG - 5 ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-87AE9A514306</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>CLARITINE 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-E7F2FD925953</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1216,6 +1231,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>CLARITINE 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-A341A31A4C87</t>
         </is>
       </c>
@@ -1239,7 +1259,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1406,6 +1426,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>CLARINASE 5MG+60MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-227B0DAC8A23</t>
         </is>
       </c>
@@ -1429,7 +1454,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1596,6 +1621,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>CLARIMAC 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-787FEBF5B9A2</t>
         </is>
       </c>
@@ -1619,7 +1649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1782,6 +1812,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>CLARIDAR</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-69AEC4A4CD7A</t>
         </is>
       </c>
@@ -1805,7 +1840,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1972,6 +2007,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>CLARITT 250 MG FILM COATED</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-B14ED1F28E46</t>
         </is>
       </c>
@@ -1995,7 +2035,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2154,6 +2194,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>CLARAZOLE 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-8EE2FA6C201F</t>
         </is>
       </c>
@@ -2177,7 +2222,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2340,6 +2385,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>CLARA 5MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-F381B439F397</t>
         </is>
       </c>
@@ -2363,7 +2413,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2530,6 +2580,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>CLARA 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-52A945976945</t>
         </is>
       </c>
@@ -2553,7 +2608,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2716,6 +2771,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>CLARAZOLE 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-68D8F458BE7B</t>
         </is>
       </c>
@@ -2739,7 +2799,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2898,6 +2958,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>CLORACEF 375MG- 5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-05258A9C05B2</t>
         </is>
       </c>
@@ -2921,7 +2986,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3092,6 +3157,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>CONCOR COR</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-598E0394D5AA</t>
         </is>
       </c>
@@ -3115,7 +3185,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3290,6 +3360,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CONCOR 5 PLUS F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-21BF4F26C4DA</t>
         </is>
       </c>
@@ -3313,7 +3388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3488,6 +3563,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-583B3BA4B188</t>
         </is>
       </c>
@@ -3511,7 +3591,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3686,6 +3766,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-CC5DC26CBF12</t>
         </is>
       </c>
@@ -3709,7 +3794,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3876,6 +3961,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>CONCERTA EXTENDED RELEASE 36MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-764CE7C5E02A</t>
         </is>
       </c>
@@ -3899,7 +3989,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4066,6 +4156,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CONCERTA EXTENDED RELEASE 18MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-786281EB9ADF</t>
         </is>
       </c>
@@ -4089,7 +4184,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4248,6 +4343,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>CONAZOLE VAGINAL CREAM 20MG-1GM</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-1684546FE60E</t>
         </is>
       </c>
@@ -4271,7 +4371,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4442,6 +4542,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>CONAZOLE VAGINAL CREAM 20MG-1GM</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-7FB7AE8C99C0</t>
         </is>
       </c>
@@ -4465,7 +4570,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4624,6 +4729,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>CONAZOL 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-A3EFF9ED1BD5</t>
         </is>
       </c>
@@ -4647,7 +4757,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4814,6 +4924,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CONTRACTUBEX</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-20E5046C5981</t>
         </is>
       </c>
@@ -4837,7 +4952,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5008,6 +5123,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>CONTRACTUBEX</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-676DA355C269</t>
         </is>
       </c>
@@ -5031,7 +5151,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5204,6 +5324,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>COVERAM 5MG-10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-6A8564BAC396</t>
         </is>
       </c>
@@ -5227,7 +5352,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5404,6 +5529,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>COVERAM 10MG-5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-33D0E340BC9B</t>
         </is>
       </c>
@@ -5427,7 +5557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5600,6 +5730,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>COVERAM 10MG-10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-B4AD81546FDE</t>
         </is>
       </c>
@@ -5623,7 +5758,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5794,6 +5929,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>CO-TABUVAN</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-AD3F83CFAE93</t>
         </is>
       </c>
@@ -5817,7 +5957,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5984,6 +6124,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>CO-TABUVAN</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-63359A58B3C8</t>
         </is>
       </c>
@@ -6007,7 +6152,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6170,6 +6315,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>CONAZOL 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-817CF3111B06</t>
         </is>
       </c>
@@ -6193,7 +6343,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6356,6 +6506,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>CO-TABUVAN</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-F629B063975B</t>
         </is>
       </c>
@@ -6379,7 +6534,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6550,6 +6705,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>CO-TABUVAN</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-E24AAF18F6D3</t>
         </is>
       </c>
@@ -6573,7 +6733,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6736,6 +6896,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CORTIDERM 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-E556E84D3F88</t>
         </is>
       </c>
@@ -6759,7 +6924,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6922,6 +7087,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>CORTIDERM 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-7B72C6DF6954</t>
         </is>
       </c>
@@ -6945,7 +7115,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7108,6 +7278,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CO-RENITEC</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-8262167D7744</t>
         </is>
       </c>
@@ -7131,7 +7306,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7294,6 +7469,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>COPEGUS 200 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-B2120D4E68C8</t>
         </is>
       </c>
@@ -7317,7 +7497,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7480,6 +7660,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CO-TABUVAN</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-D2393DF48F6B</t>
         </is>
       </c>
@@ -7503,7 +7688,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7666,6 +7851,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CLORACEF FORTE</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-03A050AD5FE2</t>
         </is>
       </c>
@@ -7689,7 +7879,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7856,6 +8046,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>COBAL 500MCG TAB</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-D52761387818</t>
         </is>
       </c>
@@ -7879,7 +8074,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8048,6 +8243,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Co-Aprovel 150-12.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-91C12AADD21C</t>
         </is>
       </c>
@@ -8071,7 +8271,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8234,6 +8434,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>CO-DIOVAN</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-8CF5390B4726</t>
         </is>
       </c>
@@ -8257,7 +8462,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8424,6 +8629,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>CO-DIOVAN</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-9EBCD13725D5</t>
         </is>
       </c>
@@ -8447,7 +8657,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8614,6 +8824,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>CO AMOX  1000MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-10B9DE0224B0</t>
         </is>
       </c>
@@ -8637,7 +8852,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8796,6 +9011,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>CLOVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-5FB387D1FA91</t>
         </is>
       </c>
@@ -8819,7 +9039,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8982,6 +9202,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>CLOVIR 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-AC669750D05F</t>
         </is>
       </c>
@@ -9005,7 +9230,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9168,6 +9393,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>CLOVAINE 10% W/W GEL</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-C937D260FB21</t>
         </is>
       </c>
@@ -9191,7 +9421,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9362,6 +9592,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>CLOTRIZOLE 100MG VAGINAL TABLETS</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-7CD5C913B135</t>
         </is>
       </c>
@@ -9385,7 +9620,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9560,6 +9795,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>CLOTRIM 100 MG VAGINAL TABLETS</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-C4C91DCE3392</t>
         </is>
       </c>
@@ -9583,7 +9823,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9746,6 +9986,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>CLOTREX</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-28A09DB15685</t>
         </is>
       </c>
@@ -9769,7 +10014,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9940,6 +10185,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>CO-DIOVAN</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-859C6CF58BA1</t>
         </is>
       </c>
@@ -9963,7 +10213,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10126,6 +10376,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>CO-DIOVAN</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-C8AF9AAD4B02</t>
         </is>
       </c>
@@ -10149,7 +10404,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10316,6 +10571,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>CO-DIOVAN</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-EBD6E0011012</t>
         </is>
       </c>
@@ -10339,7 +10599,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10502,6 +10762,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>COMPOUND SODIUM LACTATE INF.</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-F4E3141B0F03</t>
         </is>
       </c>
@@ -10525,7 +10790,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10684,6 +10949,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>COMPOUND SODIUM LACTATE INF.</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-F4569661E27C</t>
         </is>
       </c>
@@ -10707,7 +10977,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10870,6 +11140,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>COMPOUND SODIUM LACTATE INF.</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-2F19239714A0</t>
         </is>
       </c>
@@ -10893,7 +11168,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11068,6 +11343,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>COMBIVIR F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-43A730ABC8EF</t>
         </is>
       </c>
@@ -11091,7 +11371,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11254,6 +11534,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>COLPERMIN 187MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-9CBB0207D161</t>
         </is>
       </c>
@@ -11277,7 +11562,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11436,6 +11721,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>COLOPATHIL3.39 G SACHET</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-2D16957D3E8A</t>
         </is>
       </c>
@@ -11459,7 +11749,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11622,6 +11912,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>COLI-URINAL effervescent granules</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-A7AD52E73EB6</t>
         </is>
       </c>
@@ -11645,7 +11940,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11812,6 +12107,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>COMBIGAN</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-3778C6781C91</t>
         </is>
       </c>
@@ -11835,7 +12135,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12008,6 +12308,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>COVERAM 5MG-5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-C5AF1CD63C6D</t>
         </is>
       </c>
@@ -12031,7 +12336,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12194,6 +12499,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>CIPROXEN 750MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-DE8D8BBB29FB</t>
         </is>
       </c>
@@ -12217,7 +12527,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12388,6 +12698,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>CIPROXEN 250MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-C3A5E8EE740B</t>
         </is>
       </c>
@@ -12411,7 +12726,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12578,6 +12893,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>CEFUREX 250MG-5ML POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-BFBD4827FEE6</t>
         </is>
       </c>
@@ -12601,7 +12921,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12768,6 +13088,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t xml:space="preserve">CEFUREX 250MG F-C TABLETS </t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-4DFE8B144830</t>
         </is>
       </c>
@@ -12791,7 +13116,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12958,6 +13283,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>CEFUREX 125MG-5ML POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-4962CAE02057</t>
         </is>
       </c>
@@ -12981,7 +13311,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13144,6 +13474,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>CEFRAX 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-EB2177D7AAAA</t>
         </is>
       </c>
@@ -13167,7 +13502,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13326,6 +13661,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>CEFRAX 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-1098D6152E03</t>
         </is>
       </c>
@@ -13349,7 +13689,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13508,6 +13848,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>CEFRAX 100MG/5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-19A753F62F0D</t>
         </is>
       </c>
@@ -13531,7 +13876,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13698,6 +14043,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>CEFRAMED 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-24A58B8B6C13</t>
         </is>
       </c>
@@ -13721,7 +14071,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13896,6 +14246,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>CEFPROZ 250MG-5ML POWDR FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-E61846CB6701</t>
         </is>
       </c>
@@ -13919,7 +14274,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14086,6 +14441,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>CEFPROZ 250MG/5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-94C42C640EF2</t>
         </is>
       </c>
@@ -14109,7 +14469,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14272,6 +14632,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t xml:space="preserve">CEFUREX 500MG F-C TABLETS </t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-D5616BA10AA3</t>
         </is>
       </c>
@@ -14295,7 +14660,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14462,6 +14827,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>CEFUTIL 250MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-1A0E4B1F5580</t>
         </is>
       </c>
@@ -14485,7 +14855,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14656,6 +15026,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>CEFUTIL 500 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-1AB9217B0339</t>
         </is>
       </c>
@@ -14679,7 +15054,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14842,6 +15217,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CEPHALEX ORAL SUSP 250MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-27734FAB1149</t>
         </is>
       </c>
@@ -14865,7 +15245,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15032,6 +15412,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>CEPHALEX 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-3A4039A29D58</t>
         </is>
       </c>
@@ -15055,7 +15440,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15218,6 +15603,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>CEFPROZ 125MG-5ML POWDER FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-28AB1486FB68</t>
         </is>
       </c>
@@ -15241,7 +15631,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15404,6 +15794,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>CEPHADAR CAPSULES 250MG</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-A8B736F3C267</t>
         </is>
       </c>
@@ -15427,7 +15822,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15588,6 +15983,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>CENTRUM TABLET (ADVANCED FORMULA)</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-FB7E3DEA3555</t>
         </is>
       </c>
@@ -15611,7 +16011,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15770,6 +16170,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>CELSENTRI 300MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-CB76CC2CD5D9</t>
         </is>
       </c>
@@ -15793,7 +16198,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15952,6 +16357,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>CELSENTRI 150MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-6EC0B714CFFF</t>
         </is>
       </c>
@@ -15975,7 +16385,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16142,6 +16552,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>CELLCEPT 250 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-761FC943057E</t>
         </is>
       </c>
@@ -16165,7 +16580,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16336,6 +16751,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>CEPHADAR</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-E47D0681AC3C</t>
         </is>
       </c>
@@ -16359,7 +16779,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16534,6 +16954,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>CEFODOX 200 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-8DFA4CB86F24</t>
         </is>
       </c>
@@ -16557,7 +16982,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16720,6 +17145,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>CEFAMAX 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-E23841B47F80</t>
         </is>
       </c>
@@ -16743,7 +17173,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16902,6 +17332,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>CEFAMAX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-96BE0A4FC225</t>
         </is>
       </c>
@@ -16925,7 +17360,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17088,6 +17523,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>CEFADROX 500MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-06F27659B2BD</t>
         </is>
       </c>
@@ -17111,7 +17551,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17270,6 +17710,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>CEFADROX 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-432330329AB6</t>
         </is>
       </c>
@@ -17293,7 +17738,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17456,6 +17901,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>CEFADROX 250MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-C2AEF74C9BA4</t>
         </is>
       </c>
@@ -17479,7 +17929,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17646,6 +18096,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>CEECAL EFFERVESCENT TABLETS</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-E5B818E3E219</t>
         </is>
       </c>
@@ -17669,7 +18124,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17836,6 +18291,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>CECLOR MR 750 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-97BC1CCC9D07</t>
         </is>
       </c>
@@ -17859,7 +18319,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18018,6 +18478,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>CECLOR MR 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-3C44CA6B7E7B</t>
         </is>
       </c>
@@ -18041,7 +18506,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18200,6 +18665,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CECLOR MR 375 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-070182338D35</t>
         </is>
       </c>
@@ -18223,7 +18693,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18390,6 +18860,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>CECLOR 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-25E7CB4549B5</t>
         </is>
       </c>
@@ -18413,7 +18888,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18576,6 +19051,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>CECLOR 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-8AA034ED051C</t>
         </is>
       </c>
@@ -18599,7 +19079,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18770,6 +19250,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>CECLOR 250 MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-3170A2217BB8</t>
         </is>
       </c>
@@ -18793,7 +19278,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18964,6 +19449,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>CEFODOX 100MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-2DFA47951BEC</t>
         </is>
       </c>
@@ -18987,7 +19477,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19154,6 +19644,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>CEFIX 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-23B13A3DDA76</t>
         </is>
       </c>
@@ -19177,7 +19672,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19348,6 +19843,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>CEFIX 100MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-678AC5D422F3</t>
         </is>
       </c>
@@ -19371,7 +19871,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19537,6 +20037,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>CEFIM 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-0413427E7DDC</t>
         </is>
@@ -19553,7 +20058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19599,100 +20104,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19724,7 +20234,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19739,92 +20249,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-40895</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>182.07</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>37</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19856,7 +20371,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19871,92 +20386,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-58903</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>394.94</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>38</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19988,7 +20508,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20003,92 +20523,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-55870</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>195.19</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Medical Bed / Mattress</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20120,7 +20645,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20135,92 +20660,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-64898</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>330.5</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Medical Bed / Mattress</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>40</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20252,7 +20782,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20267,92 +20797,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-75466</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>154.11</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>41</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20384,7 +20919,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20399,92 +20934,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-47476</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>498</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>42</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20516,7 +21056,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20531,92 +21071,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-61566</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>252.27</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>43</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20648,7 +21193,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20663,92 +21208,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-82826</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>262.42</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>44</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20780,7 +21330,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20795,92 +21345,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-94771</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>45</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20912,7 +21467,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20927,92 +21482,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-61647</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>448.49</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>46</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21044,7 +21604,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21059,92 +21619,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-58482</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>264.41</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>47</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21176,7 +21741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21191,92 +21756,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-73548</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>364.46</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>48</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21293,7 +21863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21399,6 +21969,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21434,7 +22014,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21499,6 +22079,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-9E1F3AEB9B09</t>
         </is>
@@ -21535,7 +22125,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21600,6 +22190,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-B0AE555D696E</t>
         </is>
@@ -21636,7 +22236,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21701,6 +22301,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-E56B9FDB7AFE</t>
         </is>
@@ -21737,7 +22347,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21802,6 +22412,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-C08D39B32FF8</t>
         </is>
@@ -21838,7 +22458,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21903,6 +22523,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-84A9EB56ECA7</t>
         </is>
@@ -21939,7 +22569,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22004,6 +22634,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-5A9FE679F9D9</t>
         </is>
@@ -22040,7 +22680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22105,6 +22745,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-B7E5B6E48017</t>
         </is>
@@ -22141,7 +22791,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22206,6 +22856,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-04CAD8CD01B5</t>
         </is>
@@ -22242,7 +22902,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22307,6 +22967,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-34E9DCAB8ABA</t>
         </is>
@@ -22343,7 +23013,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22408,6 +23078,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-3BCD7DB03535</t>
         </is>
@@ -22444,7 +23124,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22509,6 +23189,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-E80A5AF9EDF1</t>
         </is>
@@ -22545,7 +23235,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22610,6 +23300,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-8099EB48216F</t>
         </is>
@@ -22646,7 +23346,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22711,6 +23411,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CDB111230F40</t>
         </is>
@@ -22747,7 +23457,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22812,6 +23522,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-60E97E34AA35</t>
         </is>
@@ -22848,7 +23568,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22913,6 +23633,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-D3658EC48E21</t>
         </is>
@@ -22949,7 +23679,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23014,6 +23744,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-C9782A67D062</t>
         </is>
@@ -23050,7 +23790,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23115,6 +23855,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-06F8F65B3627</t>
         </is>
@@ -23151,7 +23901,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23216,6 +23966,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-C6147A984122</t>
         </is>
@@ -23252,7 +24012,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23317,6 +24077,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-BC60C38560FC</t>
         </is>
@@ -23353,7 +24123,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23418,6 +24188,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-02705C088F3A</t>
         </is>

--- a/product_upload/packages/13/file.xlsx
+++ b/product_upload/packages/13/file.xlsx
@@ -686,8 +686,16 @@
           <t>0501518222-448-371394625431</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARITT 125 MG - 5 ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CLARITT 125 MG - 5 ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1267,8 +1275,16 @@
           <t>0754991156-224-337926417084</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARINASE 5MG+60MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CLARINASE 5MG+60MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1657,8 +1673,16 @@
           <t>5716780924-848-466198229411</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARIDAR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CLARIDAR detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2043,8 +2067,16 @@
           <t>5805201051-770-094408899964</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARAZOLE 2% CREAM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CLARAZOLE 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2616,8 +2648,16 @@
           <t>6206742382-187-344287878985</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARAZOLE 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CLARAZOLE 2% SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2807,8 +2847,16 @@
           <t>1069900787-456-157859444500</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLORACEF 375MG- 5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CLORACEF 375MG- 5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -4192,8 +4240,16 @@
           <t>3878635495-427-262263495861</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CONAZOLE VAGINAL CREAM 20MG-1GM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CONAZOLE VAGINAL CREAM 20MG-1GM detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4578,8 +4634,16 @@
           <t>4115183295-711-749974196408</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CONAZOL 2% CREAM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CONAZOL 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -6160,8 +6224,16 @@
           <t>4204161028-004-838074210260</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CONAZOL 2% CREAM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CONAZOL 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6741,8 +6813,16 @@
           <t>4647926757-742-978546784988</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CORTIDERM 1% CREAM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CORTIDERM 1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7123,8 +7203,16 @@
           <t>2838016460-365-685139596488</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-RENITEC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CO-RENITEC detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7314,8 +7402,16 @@
           <t>6933159513-678-756815847431</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COPEGUS 200 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>COPEGUS 200 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7696,8 +7792,16 @@
           <t>7628496636-621-027988496018</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLORACEF FORTE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CLORACEF FORTE detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8665,8 +8769,16 @@
           <t>7664257071-007-868260613254</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO AMOX  1000MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CO AMOX  1000MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8860,8 +8972,16 @@
           <t>8421111554-821-791732564102</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CLOVIR 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9047,8 +9167,16 @@
           <t>9259283706-840-469971316253</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOVIR 200MG TAB</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CLOVIR 200MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9238,8 +9366,16 @@
           <t>8810350998-702-151983533386</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOVAINE 10% W/W GEL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CLOVAINE 10% W/W GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9831,8 +9967,16 @@
           <t>5894642185-246-103679599872</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOTREX</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CLOTREX detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10607,8 +10751,16 @@
           <t>8187898371-976-002879673218</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMPOUND SODIUM LACTATE INF.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COMPOUND SODIUM LACTATE INF. detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10798,8 +10950,16 @@
           <t>0587913672-335-981311744391</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMPOUND SODIUM LACTATE INF.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>COMPOUND SODIUM LACTATE INF. detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10985,8 +11145,16 @@
           <t>5972247659-869-696196264919</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMPOUND SODIUM LACTATE INF.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COMPOUND SODIUM LACTATE INF. detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11570,8 +11738,16 @@
           <t>7177736546-800-844328242665</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COLOPATHIL3.39 G SACHET</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>COLOPATHIL3.39 G SACHET detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11948,8 +12124,16 @@
           <t>9975590174-862-578712616863</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COMBIGAN</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMBIGAN detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12734,8 +12918,16 @@
           <t>4009725500-005-749490036727</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUREX 250MG-5ML POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CEFUREX 250MG-5ML POWDER FOR SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12929,8 +13121,16 @@
           <t>4418675694-342-289556627962</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUREX 250MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CEFUREX 250MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13124,8 +13324,16 @@
           <t>2459797056-842-269926200588</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUREX 125MG-5ML POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CEFUREX 125MG-5ML POWDER FOR SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13319,8 +13527,16 @@
           <t>4846355033-138-169704354094</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFRAX 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CEFRAX 400MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13510,8 +13726,16 @@
           <t>5651524975-361-034007551198</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFRAX 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CEFRAX 200MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13697,8 +13921,16 @@
           <t>5015182281-936-654997422361</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFRAX 100MG/5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CEFRAX 100MG/5ML POWDER FOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13884,8 +14116,16 @@
           <t>6423517571-184-969354787595</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFRAMED 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CEFRAMED 500MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14477,8 +14717,16 @@
           <t>8014221796-745-673001858521</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUREX 500MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CEFUREX 500MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -15062,8 +15310,16 @@
           <t>3134285132-613-814686169133</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEPHALEX ORAL SUSP 250MG-5ML</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CEPHALEX ORAL SUSP 250MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15448,8 +15704,16 @@
           <t>7408219865-054-241571073485</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFPROZ 125MG-5ML POWDER FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CEFPROZ 125MG-5ML POWDER FOR ORAL SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15830,8 +16094,16 @@
           <t>9395318383-757-978320392491</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CENTRUM TABLET (ADVANCED FORMULA)</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CENTRUM TABLET (ADVANCED FORMULA) detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16019,8 +16291,16 @@
           <t>0396300103-833-591888186188</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELSENTRI 300MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CELSENTRI 300MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16206,8 +16486,16 @@
           <t>5896864075-211-917210028173</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELSENTRI 150MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CELSENTRI 150MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16990,8 +17278,16 @@
           <t>3656577924-011-722323649042</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFAMAX 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CEFAMAX 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17181,8 +17477,16 @@
           <t>9824883619-458-625924509309</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFAMAX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CEFAMAX 200MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17368,8 +17672,16 @@
           <t>3648219523-529-973943181115</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFADROX 500MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CEFADROX 500MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17559,8 +17871,16 @@
           <t>3180514881-129-044795748446</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFADROX 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CEFADROX 500MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17746,8 +18066,16 @@
           <t>6345860872-710-623493797975</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFADROX 250MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CEFADROX 250MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17937,8 +18265,16 @@
           <t>7303797011-280-699951344387</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEECAL EFFERVESCENT TABLETS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CEECAL EFFERVESCENT TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18327,8 +18663,16 @@
           <t>4919391028-910-858294391918</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CECLOR MR 500MG TAB</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CECLOR MR 500MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18514,8 +18858,16 @@
           <t>3313901641-829-830380639495</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CECLOR MR 375 MG TAB</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CECLOR MR 375 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18896,8 +19248,16 @@
           <t>3383637002-713-238951698385</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CECLOR 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CECLOR 250MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19485,8 +19845,16 @@
           <t>9979789200-392-040760415328</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFIX 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CEFIX 200MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/13/file.xlsx
+++ b/product_upload/packages/13/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22231,7 +22231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22312,40 +22312,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22425,38 +22430,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>295.24</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-9E1F3AEB9B09</t>
         </is>
@@ -22536,38 +22546,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>241.82</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-B0AE555D696E</t>
         </is>
@@ -22647,38 +22662,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>163.14</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-E56B9FDB7AFE</t>
         </is>
@@ -22758,38 +22778,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>408.11</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-C08D39B32FF8</t>
         </is>
@@ -22869,38 +22894,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>207.36</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-84A9EB56ECA7</t>
         </is>
@@ -22980,38 +23010,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>355.24</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-5A9FE679F9D9</t>
         </is>
@@ -23091,38 +23126,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>289.56</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-B7E5B6E48017</t>
         </is>
@@ -23202,38 +23242,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>493.39</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-04CAD8CD01B5</t>
         </is>
@@ -23313,38 +23358,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>187.13</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-34E9DCAB8ABA</t>
         </is>
@@ -23424,38 +23474,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>147.25</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-3BCD7DB03535</t>
         </is>
@@ -23535,38 +23590,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>419.82</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-E80A5AF9EDF1</t>
         </is>
@@ -23646,38 +23706,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>248.5</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-8099EB48216F</t>
         </is>
@@ -23757,38 +23822,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>79.15000000000001</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CDB111230F40</t>
         </is>
@@ -23868,38 +23938,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>162.21</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-60E97E34AA35</t>
         </is>
@@ -23979,38 +24054,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>62.14</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-D3658EC48E21</t>
         </is>
@@ -24090,38 +24170,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>319.17</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-C9782A67D062</t>
         </is>
@@ -24201,38 +24286,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>449.89</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-06F8F65B3627</t>
         </is>
@@ -24312,38 +24402,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>255.16</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-C6147A984122</t>
         </is>
@@ -24423,38 +24518,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>255.75</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-BC60C38560FC</t>
         </is>
@@ -24534,38 +24634,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>290.37</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-02705C088F3A</t>
         </is>
